--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:16:08+00:00</t>
+    <t>2026-09-29T14:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T14:28:05+00:00</t>
+    <t>2026-09-30T20:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:36:50+00:00</t>
+    <t>2026-10-01T12:23:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
